--- a/dist/tally_templates/SWSP.xlsx
+++ b/dist/tally_templates/SWSP.xlsx
@@ -1117,7 +1117,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac x16r2">
   <numFmts count="11">
     <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * -#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* (#,##0);_(* &quot;-&quot;_);_(@_)"/>
@@ -3158,7 +3158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="616">
+  <cellXfs count="651">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -4986,6 +4986,111 @@
     </xf>
     <xf numFmtId="174" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4994,11 +5099,11 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <ns3:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <ns4:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -5266,7 +5371,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -6070,14 +6175,14 @@
       <c r="D8" s="373" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="194">
+      <c r="E8" s="171">
         <v>7</v>
       </c>
       <c r="F8" s="194"/>
       <c r="G8" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="14" t="s">
+      <c r="H8" s="621" t="s">
         <v>99</v>
       </c>
       <c r="I8" s="14"/>
@@ -6985,15 +7090,15 @@
       <c r="Y40" s="1"/>
     </row>
     <row r="41" ht="15.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A41" s="208"/>
-      <c r="B41" s="208"/>
+      <c r="A41" s="648"/>
+      <c r="B41" s="648"/>
       <c r="C41" s="3"/>
-      <c r="D41" s="208"/>
-      <c r="E41" s="208"/>
-      <c r="F41" s="208"/>
+      <c r="D41" s="648"/>
+      <c r="E41" s="648"/>
+      <c r="F41" s="648"/>
       <c r="G41" s="3"/>
-      <c r="H41" s="208"/>
-      <c r="I41" s="208"/>
+      <c r="H41" s="648"/>
+      <c r="I41" s="648"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
@@ -8161,7 +8266,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
     <pageSetUpPr fitToPage="1"/>
@@ -8960,7 +9065,7 @@
       <c r="A8" s="213" t="s">
         <v>64</v>
       </c>
-      <c r="B8" s="213" t="s">
+      <c r="B8" s="171" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="213"/>
@@ -8972,7 +9077,7 @@
         <v>41</v>
       </c>
       <c r="I8" s="194"/>
-      <c r="J8" s="194" t="s">
+      <c r="J8" s="171" t="s">
         <v>66</v>
       </c>
       <c r="K8" s="194"/>
@@ -9023,7 +9128,7 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
-    <row r="10" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="219" t="s">
         <v>11</v>
       </c>
@@ -9064,7 +9169,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
-    <row r="11" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="225"/>
       <c r="B11" s="225"/>
       <c r="C11" s="226"/>
@@ -9881,7 +9986,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
     <pageSetUpPr fitToPage="1"/>
@@ -10238,7 +10343,7 @@
       <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="616" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="1"/>
@@ -10247,14 +10352,14 @@
       <c r="F4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="12"/>
+      <c r="G4" s="617"/>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
       <c r="J4" s="1"/>
       <c r="K4" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="L4" s="13"/>
+      <c r="L4" s="618"/>
       <c r="M4" s="14"/>
       <c r="N4" s="14"/>
       <c r="O4" s="14"/>
@@ -10300,21 +10405,21 @@
       <c r="A6" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="16"/>
+      <c r="B6" s="617"/>
       <c r="C6" s="1"/>
       <c r="D6" s="2"/>
       <c r="E6" s="17"/>
       <c r="F6" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="12"/>
+      <c r="G6" s="617"/>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
       <c r="J6" s="1"/>
       <c r="K6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="L6" s="18" t="s">
+      <c r="L6" s="619" t="s">
         <v>9</v>
       </c>
       <c r="M6" s="18"/>
@@ -13026,7 +13131,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
@@ -13705,7 +13810,7 @@
       <c r="O6" s="266" t="s">
         <v>4</v>
       </c>
-      <c r="P6" s="40"/>
+      <c r="P6" s="649"/>
       <c r="Q6" s="40"/>
       <c r="R6" s="90" t="str">
         <f>'Final Work'!G4</f>
@@ -13779,7 +13884,7 @@
       </c>
       <c r="B8" s="412"/>
       <c r="C8" s="412"/>
-      <c r="D8" s="413" t="s">
+      <c r="D8" s="650" t="s">
         <v>66</v>
       </c>
       <c r="E8" s="413"/>
@@ -13795,7 +13900,7 @@
       <c r="O8" s="413" t="s">
         <v>7</v>
       </c>
-      <c r="P8" s="155"/>
+      <c r="P8" s="650"/>
       <c r="Q8" s="155"/>
       <c r="R8" s="412">
         <f>'Final Work'!G6</f>
@@ -13812,7 +13917,7 @@
       </c>
       <c r="Z8" s="412"/>
       <c r="AA8" s="412"/>
-      <c r="AB8" s="412" t="s">
+      <c r="AB8" s="650" t="s">
         <v>25</v>
       </c>
       <c r="AC8" s="412"/>
@@ -19927,7 +20032,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="60"/>
     <pageSetUpPr fitToPage="1"/>
@@ -20732,13 +20837,13 @@
       <c r="G6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H6" s="194"/>
+      <c r="H6" s="171"/>
       <c r="I6" s="194"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="13"/>
+      <c r="L6" s="618"/>
       <c r="M6" s="14"/>
       <c r="N6" s="9"/>
       <c r="O6" s="9"/>
@@ -20784,7 +20889,7 @@
       <c r="A8" s="213" t="s">
         <v>58</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="632" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="3"/>
@@ -20794,13 +20899,13 @@
       <c r="G8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H8" s="194"/>
+      <c r="H8" s="171"/>
       <c r="I8" s="194"/>
       <c r="J8" s="3"/>
       <c r="K8" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="L8" s="194"/>
+      <c r="L8" s="171"/>
       <c r="M8" s="194"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
@@ -20842,7 +20947,7 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
-    <row r="10" ht="14.45" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="267" t="s">
         <v>43</v>
       </c>
@@ -20887,7 +20992,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
-    <row r="11" ht="14.45" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="222"/>
       <c r="B11" s="223"/>
       <c r="C11" s="224"/>
@@ -20920,16 +21025,16 @@
       <c r="A12" s="268"/>
       <c r="B12" s="269"/>
       <c r="C12" s="270"/>
-      <c r="D12" s="271"/>
-      <c r="E12" s="272"/>
-      <c r="F12" s="273"/>
+      <c r="D12" s="269"/>
+      <c r="E12" s="326"/>
+      <c r="F12" s="270"/>
       <c r="G12" s="268"/>
       <c r="H12" s="274"/>
       <c r="I12" s="275"/>
       <c r="J12" s="262"/>
       <c r="K12" s="259"/>
       <c r="L12" s="268"/>
-      <c r="M12" s="276"/>
+      <c r="M12" s="638"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -20944,19 +21049,19 @@
       <c r="Y12" s="3"/>
     </row>
     <row r="13" ht="19.15" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A13" s="277"/>
+      <c r="A13" s="639"/>
       <c r="B13" s="278"/>
       <c r="C13" s="92"/>
-      <c r="D13" s="279"/>
-      <c r="E13" s="280"/>
-      <c r="F13" s="281"/>
+      <c r="D13" s="286"/>
+      <c r="E13" s="640"/>
+      <c r="F13" s="641"/>
       <c r="G13" s="259"/>
       <c r="H13" s="282"/>
       <c r="I13" s="283"/>
       <c r="J13" s="262"/>
       <c r="K13" s="259"/>
       <c r="L13" s="259"/>
-      <c r="M13" s="284"/>
+      <c r="M13" s="642"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
@@ -20971,19 +21076,19 @@
       <c r="Y13" s="3"/>
     </row>
     <row r="14" ht="19.15" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A14" s="285"/>
+      <c r="A14" s="643"/>
       <c r="B14" s="286"/>
       <c r="C14" s="207"/>
-      <c r="D14" s="279"/>
-      <c r="E14" s="280"/>
-      <c r="F14" s="281"/>
+      <c r="D14" s="286"/>
+      <c r="E14" s="640"/>
+      <c r="F14" s="641"/>
       <c r="G14" s="259"/>
       <c r="H14" s="260"/>
       <c r="I14" s="287"/>
       <c r="J14" s="262"/>
       <c r="K14" s="259"/>
       <c r="L14" s="259"/>
-      <c r="M14" s="288"/>
+      <c r="M14" s="644"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
@@ -20998,19 +21103,19 @@
       <c r="Y14" s="3"/>
     </row>
     <row r="15" ht="19.15" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A15" s="285"/>
+      <c r="A15" s="643"/>
       <c r="B15" s="286"/>
       <c r="C15" s="207"/>
-      <c r="D15" s="279"/>
-      <c r="E15" s="280"/>
-      <c r="F15" s="281"/>
+      <c r="D15" s="286"/>
+      <c r="E15" s="640"/>
+      <c r="F15" s="641"/>
       <c r="G15" s="259"/>
       <c r="H15" s="260"/>
       <c r="I15" s="287"/>
       <c r="J15" s="262"/>
       <c r="K15" s="259"/>
       <c r="L15" s="259"/>
-      <c r="M15" s="288"/>
+      <c r="M15" s="644"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
@@ -21025,19 +21130,19 @@
       <c r="Y15" s="3"/>
     </row>
     <row r="16" ht="19.15" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A16" s="285"/>
+      <c r="A16" s="643"/>
       <c r="B16" s="286"/>
       <c r="C16" s="207"/>
-      <c r="D16" s="279"/>
-      <c r="E16" s="280"/>
-      <c r="F16" s="281"/>
+      <c r="D16" s="286"/>
+      <c r="E16" s="640"/>
+      <c r="F16" s="641"/>
       <c r="G16" s="259"/>
       <c r="H16" s="260"/>
       <c r="I16" s="287"/>
       <c r="J16" s="262"/>
       <c r="K16" s="259"/>
       <c r="L16" s="259"/>
-      <c r="M16" s="288"/>
+      <c r="M16" s="644"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
@@ -21052,19 +21157,19 @@
       <c r="Y16" s="3"/>
     </row>
     <row r="17" ht="24.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A17" s="285"/>
+      <c r="A17" s="643"/>
       <c r="B17" s="228"/>
       <c r="C17" s="229"/>
-      <c r="D17" s="243"/>
-      <c r="E17" s="230"/>
-      <c r="F17" s="231"/>
+      <c r="D17" s="228"/>
+      <c r="E17" s="633"/>
+      <c r="F17" s="634"/>
       <c r="G17" s="232"/>
       <c r="H17" s="233"/>
       <c r="I17" s="234"/>
       <c r="J17" s="235"/>
       <c r="K17" s="232"/>
       <c r="L17" s="232"/>
-      <c r="M17" s="289"/>
+      <c r="M17" s="645"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
@@ -21079,19 +21184,19 @@
       <c r="Y17" s="3"/>
     </row>
     <row r="18" ht="24.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A18" s="285"/>
+      <c r="A18" s="643"/>
       <c r="B18" s="228"/>
       <c r="C18" s="229"/>
-      <c r="D18" s="243"/>
-      <c r="E18" s="230"/>
-      <c r="F18" s="231"/>
+      <c r="D18" s="228"/>
+      <c r="E18" s="633"/>
+      <c r="F18" s="634"/>
       <c r="G18" s="232"/>
       <c r="H18" s="233"/>
       <c r="I18" s="234"/>
       <c r="J18" s="235"/>
       <c r="K18" s="232"/>
       <c r="L18" s="232"/>
-      <c r="M18" s="289"/>
+      <c r="M18" s="645"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
@@ -21106,19 +21211,19 @@
       <c r="Y18" s="3"/>
     </row>
     <row r="19" ht="24.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A19" s="285"/>
+      <c r="A19" s="643"/>
       <c r="B19" s="228"/>
       <c r="C19" s="229"/>
-      <c r="D19" s="243"/>
-      <c r="E19" s="230"/>
-      <c r="F19" s="231"/>
+      <c r="D19" s="228"/>
+      <c r="E19" s="633"/>
+      <c r="F19" s="634"/>
       <c r="G19" s="232"/>
       <c r="H19" s="233"/>
       <c r="I19" s="234"/>
       <c r="J19" s="235"/>
       <c r="K19" s="232"/>
       <c r="L19" s="232"/>
-      <c r="M19" s="289"/>
+      <c r="M19" s="645"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
@@ -21133,19 +21238,19 @@
       <c r="Y19" s="3"/>
     </row>
     <row r="20" ht="24.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A20" s="285"/>
+      <c r="A20" s="643"/>
       <c r="B20" s="232"/>
       <c r="C20" s="232"/>
-      <c r="D20" s="243"/>
-      <c r="E20" s="230"/>
-      <c r="F20" s="231"/>
+      <c r="D20" s="228"/>
+      <c r="E20" s="633"/>
+      <c r="F20" s="634"/>
       <c r="G20" s="232"/>
       <c r="H20" s="233"/>
       <c r="I20" s="234"/>
       <c r="J20" s="235"/>
       <c r="K20" s="232"/>
       <c r="L20" s="232"/>
-      <c r="M20" s="289"/>
+      <c r="M20" s="645"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
@@ -21160,19 +21265,19 @@
       <c r="Y20" s="3"/>
     </row>
     <row r="21" ht="24.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A21" s="285"/>
+      <c r="A21" s="643"/>
       <c r="B21" s="232"/>
       <c r="C21" s="232"/>
-      <c r="D21" s="243"/>
-      <c r="E21" s="230"/>
-      <c r="F21" s="231"/>
+      <c r="D21" s="228"/>
+      <c r="E21" s="633"/>
+      <c r="F21" s="634"/>
       <c r="G21" s="232"/>
       <c r="H21" s="290"/>
       <c r="I21" s="291"/>
       <c r="J21" s="235"/>
       <c r="K21" s="232"/>
       <c r="L21" s="232"/>
-      <c r="M21" s="289"/>
+      <c r="M21" s="645"/>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
@@ -21187,19 +21292,19 @@
       <c r="Y21" s="3"/>
     </row>
     <row r="22" ht="24.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A22" s="277"/>
+      <c r="A22" s="639"/>
       <c r="B22" s="292"/>
       <c r="C22" s="293"/>
-      <c r="D22" s="243"/>
-      <c r="E22" s="230"/>
-      <c r="F22" s="231"/>
+      <c r="D22" s="228"/>
+      <c r="E22" s="633"/>
+      <c r="F22" s="634"/>
       <c r="G22" s="232"/>
       <c r="H22" s="294"/>
       <c r="I22" s="295"/>
       <c r="J22" s="235"/>
       <c r="K22" s="232"/>
       <c r="L22" s="232"/>
-      <c r="M22" s="296"/>
+      <c r="M22" s="646"/>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
@@ -21840,7 +21945,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="60"/>
     <pageSetUpPr fitToPage="1"/>
@@ -22639,7 +22744,7 @@
       <c r="A8" s="213" t="s">
         <v>64</v>
       </c>
-      <c r="B8" s="213" t="s">
+      <c r="B8" s="171" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="213"/>
@@ -22651,7 +22756,7 @@
         <v>65</v>
       </c>
       <c r="I8" s="194"/>
-      <c r="J8" s="194" t="s">
+      <c r="J8" s="171" t="s">
         <v>66</v>
       </c>
       <c r="K8" s="194"/>
@@ -22702,7 +22807,7 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
-    <row r="10" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="267" t="s">
         <v>11</v>
       </c>
@@ -22743,7 +22848,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
-    <row r="11" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="222"/>
       <c r="B11" s="222"/>
       <c r="C11" s="226"/>
@@ -25572,7 +25677,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -26239,11 +26344,11 @@
       <c r="A6" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="159"/>
+      <c r="B6" s="620"/>
       <c r="C6" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="14"/>
+      <c r="D6" s="621"/>
       <c r="E6" s="14"/>
       <c r="F6" s="9"/>
       <c r="G6" s="161" t="s">
@@ -26302,17 +26407,17 @@
       <c r="A8" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="163"/>
+      <c r="B8" s="621"/>
       <c r="C8" s="160" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="14"/>
+      <c r="D8" s="621"/>
       <c r="E8" s="14"/>
       <c r="F8" s="160"/>
       <c r="G8" s="164" t="s">
         <v>30</v>
       </c>
-      <c r="H8" s="18"/>
+      <c r="H8" s="619"/>
       <c r="I8" s="9"/>
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
@@ -26450,7 +26555,7 @@
         <v>34</v>
       </c>
       <c r="B13" s="169"/>
-      <c r="C13" s="170"/>
+      <c r="C13" s="622"/>
       <c r="D13" s="170"/>
       <c r="E13" s="170"/>
       <c r="F13" s="170"/>
@@ -26477,7 +26582,7 @@
     <row r="14" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="172"/>
       <c r="B14" s="173"/>
-      <c r="C14" s="174"/>
+      <c r="C14" s="623"/>
       <c r="D14" s="175"/>
       <c r="E14" s="175"/>
       <c r="F14" s="175"/>
@@ -26504,7 +26609,7 @@
     <row r="15" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="172"/>
       <c r="B15" s="173"/>
-      <c r="C15" s="177"/>
+      <c r="C15" s="624"/>
       <c r="D15" s="177"/>
       <c r="E15" s="177"/>
       <c r="F15" s="177"/>
@@ -26531,7 +26636,7 @@
     <row r="16" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="172"/>
       <c r="B16" s="173"/>
-      <c r="C16" s="177"/>
+      <c r="C16" s="624"/>
       <c r="D16" s="177"/>
       <c r="E16" s="177"/>
       <c r="F16" s="177"/>
@@ -26558,7 +26663,7 @@
     <row r="17" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" s="178"/>
       <c r="B17" s="179"/>
-      <c r="C17" s="180"/>
+      <c r="C17" s="625"/>
       <c r="D17" s="181"/>
       <c r="E17" s="181"/>
       <c r="F17" s="181"/>
@@ -26585,7 +26690,7 @@
     <row r="18" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="183"/>
       <c r="B18" s="184"/>
-      <c r="C18" s="185"/>
+      <c r="C18" s="626"/>
       <c r="D18" s="185"/>
       <c r="E18" s="185"/>
       <c r="F18" s="185"/>
@@ -26612,7 +26717,7 @@
     <row r="19" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="186"/>
       <c r="B19" s="179"/>
-      <c r="C19" s="180"/>
+      <c r="C19" s="625"/>
       <c r="D19" s="181"/>
       <c r="E19" s="181"/>
       <c r="F19" s="181"/>
@@ -26639,7 +26744,7 @@
     <row r="20" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="172"/>
       <c r="B20" s="179"/>
-      <c r="C20" s="174"/>
+      <c r="C20" s="623"/>
       <c r="D20" s="175"/>
       <c r="E20" s="175"/>
       <c r="F20" s="175"/>
@@ -26666,7 +26771,7 @@
     <row r="21" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="187"/>
       <c r="B21" s="179"/>
-      <c r="C21" s="174"/>
+      <c r="C21" s="623"/>
       <c r="D21" s="175"/>
       <c r="E21" s="175"/>
       <c r="F21" s="175"/>
@@ -26693,7 +26798,7 @@
     <row r="22" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" s="188"/>
       <c r="B22" s="189"/>
-      <c r="C22" s="190"/>
+      <c r="C22" s="627"/>
       <c r="D22" s="191"/>
       <c r="E22" s="191"/>
       <c r="F22" s="191"/>
@@ -26720,7 +26825,7 @@
     <row r="23" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" s="183"/>
       <c r="B23" s="179"/>
-      <c r="C23" s="193"/>
+      <c r="C23" s="628"/>
       <c r="D23" s="193"/>
       <c r="E23" s="193"/>
       <c r="F23" s="193"/>
@@ -26747,7 +26852,7 @@
     <row r="24" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" s="186"/>
       <c r="B24" s="179"/>
-      <c r="C24" s="174"/>
+      <c r="C24" s="623"/>
       <c r="D24" s="175"/>
       <c r="E24" s="175"/>
       <c r="F24" s="175"/>
@@ -26774,7 +26879,7 @@
     <row r="25" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" s="172"/>
       <c r="B25" s="179"/>
-      <c r="C25" s="174"/>
+      <c r="C25" s="623"/>
       <c r="D25" s="175"/>
       <c r="E25" s="175"/>
       <c r="F25" s="175"/>
@@ -26801,7 +26906,7 @@
     <row r="26" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" s="195"/>
       <c r="B26" s="179"/>
-      <c r="C26" s="180"/>
+      <c r="C26" s="625"/>
       <c r="D26" s="181"/>
       <c r="E26" s="181"/>
       <c r="F26" s="181"/>
@@ -26828,7 +26933,7 @@
     <row r="27" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" s="188"/>
       <c r="B27" s="179"/>
-      <c r="C27" s="196"/>
+      <c r="C27" s="629"/>
       <c r="D27" s="196"/>
       <c r="E27" s="196"/>
       <c r="F27" s="196"/>
@@ -26855,7 +26960,7 @@
     <row r="28" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" s="197"/>
       <c r="B28" s="184"/>
-      <c r="C28" s="180"/>
+      <c r="C28" s="625"/>
       <c r="D28" s="181"/>
       <c r="E28" s="181"/>
       <c r="F28" s="181"/>
@@ -26882,7 +26987,7 @@
     <row r="29" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="195"/>
       <c r="B29" s="179"/>
-      <c r="C29" s="174"/>
+      <c r="C29" s="623"/>
       <c r="D29" s="175"/>
       <c r="E29" s="175"/>
       <c r="F29" s="175"/>
@@ -26909,7 +27014,7 @@
     <row r="30" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" s="198"/>
       <c r="B30" s="179"/>
-      <c r="C30" s="174"/>
+      <c r="C30" s="623"/>
       <c r="D30" s="175"/>
       <c r="E30" s="175"/>
       <c r="F30" s="175"/>
@@ -26936,7 +27041,7 @@
     <row r="31" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="172"/>
       <c r="B31" s="179"/>
-      <c r="C31" s="180"/>
+      <c r="C31" s="625"/>
       <c r="D31" s="181"/>
       <c r="E31" s="181"/>
       <c r="F31" s="181"/>
@@ -26965,7 +27070,7 @@
         <v>35</v>
       </c>
       <c r="B32" s="179"/>
-      <c r="C32" s="174"/>
+      <c r="C32" s="623"/>
       <c r="D32" s="175"/>
       <c r="E32" s="175"/>
       <c r="F32" s="175"/>
@@ -26992,7 +27097,7 @@
     <row r="33" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="29"/>
       <c r="B33" s="184"/>
-      <c r="C33" s="199"/>
+      <c r="C33" s="630"/>
       <c r="D33" s="200"/>
       <c r="E33" s="200"/>
       <c r="F33" s="200"/>
@@ -27019,7 +27124,7 @@
     <row r="34" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" s="172"/>
       <c r="B34" s="173"/>
-      <c r="C34" s="174"/>
+      <c r="C34" s="623"/>
       <c r="D34" s="175"/>
       <c r="E34" s="175"/>
       <c r="F34" s="175"/>
@@ -27046,7 +27151,7 @@
     <row r="35" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" s="202"/>
       <c r="B35" s="179"/>
-      <c r="C35" s="193"/>
+      <c r="C35" s="628"/>
       <c r="D35" s="193"/>
       <c r="E35" s="193"/>
       <c r="F35" s="193"/>
@@ -27073,7 +27178,7 @@
     <row r="36" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" s="203"/>
       <c r="B36" s="179"/>
-      <c r="C36" s="180"/>
+      <c r="C36" s="625"/>
       <c r="D36" s="181"/>
       <c r="E36" s="181"/>
       <c r="F36" s="181"/>
@@ -27100,7 +27205,7 @@
     <row r="37" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" s="204"/>
       <c r="B37" s="205"/>
-      <c r="C37" s="190"/>
+      <c r="C37" s="627"/>
       <c r="D37" s="191"/>
       <c r="E37" s="191"/>
       <c r="F37" s="191"/>
@@ -27127,7 +27232,7 @@
     <row r="38" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" s="206"/>
       <c r="B38" s="27"/>
-      <c r="C38" s="199"/>
+      <c r="C38" s="630"/>
       <c r="D38" s="200"/>
       <c r="E38" s="200"/>
       <c r="F38" s="200"/>
@@ -27154,7 +27259,7 @@
     <row r="39" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" s="203"/>
       <c r="B39" s="56"/>
-      <c r="C39" s="177"/>
+      <c r="C39" s="624"/>
       <c r="D39" s="177"/>
       <c r="E39" s="177"/>
       <c r="F39" s="177"/>
@@ -27181,7 +27286,7 @@
     <row r="40" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40" s="203"/>
       <c r="B40" s="173"/>
-      <c r="C40" s="174"/>
+      <c r="C40" s="623"/>
       <c r="D40" s="175"/>
       <c r="E40" s="175"/>
       <c r="F40" s="175"/>
@@ -27208,7 +27313,7 @@
     <row r="41" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41" s="172"/>
       <c r="B41" s="207"/>
-      <c r="C41" s="174"/>
+      <c r="C41" s="623"/>
       <c r="D41" s="175"/>
       <c r="E41" s="175"/>
       <c r="F41" s="175"/>
@@ -27235,7 +27340,7 @@
     <row r="42" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42" s="172"/>
       <c r="B42" s="56"/>
-      <c r="C42" s="180"/>
+      <c r="C42" s="625"/>
       <c r="D42" s="181"/>
       <c r="E42" s="181"/>
       <c r="F42" s="181"/>
@@ -27505,7 +27610,7 @@
       <c r="Y51" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="41">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="C3:F3"/>
@@ -27545,6 +27650,8 @@
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="A46:B46"/>
     <mergeCell ref="G46:H46"/>
+    <mergeCell ref="C43:H43"/>
+    <mergeCell ref="C44:H44"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0.31496062992125984" footer="0.35433070866141736"/>
@@ -27553,7 +27660,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
     <pageSetUpPr fitToPage="1"/>
@@ -28358,13 +28465,13 @@
       <c r="G6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H6" s="194"/>
+      <c r="H6" s="171"/>
       <c r="I6" s="194"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="214"/>
+      <c r="L6" s="631"/>
       <c r="M6" s="214"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
@@ -28410,7 +28517,7 @@
       <c r="A8" s="213" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="632" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="215"/>
@@ -28420,13 +28527,13 @@
       <c r="G8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H8" s="194"/>
+      <c r="H8" s="171"/>
       <c r="I8" s="194"/>
       <c r="J8" s="3"/>
       <c r="K8" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="L8" s="194"/>
+      <c r="L8" s="171"/>
       <c r="M8" s="194"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
@@ -28468,7 +28575,7 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
-    <row r="10" ht="14.45" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="216" t="s">
         <v>43</v>
       </c>
@@ -28513,7 +28620,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
-    <row r="11" ht="14.45" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="222"/>
       <c r="B11" s="223"/>
       <c r="C11" s="224"/>
@@ -28547,15 +28654,15 @@
       <c r="B12" s="228"/>
       <c r="C12" s="229"/>
       <c r="D12" s="228"/>
-      <c r="E12" s="230"/>
-      <c r="F12" s="231"/>
+      <c r="E12" s="633"/>
+      <c r="F12" s="634"/>
       <c r="G12" s="232"/>
       <c r="H12" s="233"/>
       <c r="I12" s="234"/>
       <c r="J12" s="235"/>
       <c r="K12" s="232"/>
       <c r="L12" s="232"/>
-      <c r="M12" s="236"/>
+      <c r="M12" s="635"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -28574,15 +28681,15 @@
       <c r="B13" s="228"/>
       <c r="C13" s="229"/>
       <c r="D13" s="228"/>
-      <c r="E13" s="230"/>
-      <c r="F13" s="231"/>
+      <c r="E13" s="633"/>
+      <c r="F13" s="634"/>
       <c r="G13" s="232"/>
       <c r="H13" s="233"/>
       <c r="I13" s="234"/>
       <c r="J13" s="235"/>
       <c r="K13" s="232"/>
       <c r="L13" s="232"/>
-      <c r="M13" s="236"/>
+      <c r="M13" s="635"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
@@ -28601,15 +28708,15 @@
       <c r="B14" s="228"/>
       <c r="C14" s="229"/>
       <c r="D14" s="228"/>
-      <c r="E14" s="230"/>
-      <c r="F14" s="231"/>
+      <c r="E14" s="633"/>
+      <c r="F14" s="634"/>
       <c r="G14" s="232"/>
       <c r="H14" s="233"/>
       <c r="I14" s="234"/>
       <c r="J14" s="235"/>
       <c r="K14" s="232"/>
       <c r="L14" s="232"/>
-      <c r="M14" s="236"/>
+      <c r="M14" s="635"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
@@ -28628,15 +28735,15 @@
       <c r="B15" s="228"/>
       <c r="C15" s="229"/>
       <c r="D15" s="228"/>
-      <c r="E15" s="230"/>
-      <c r="F15" s="231"/>
+      <c r="E15" s="633"/>
+      <c r="F15" s="634"/>
       <c r="G15" s="232"/>
       <c r="H15" s="233"/>
       <c r="I15" s="234"/>
       <c r="J15" s="235"/>
       <c r="K15" s="232"/>
       <c r="L15" s="237"/>
-      <c r="M15" s="236"/>
+      <c r="M15" s="635"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
@@ -28655,15 +28762,15 @@
       <c r="B16" s="238"/>
       <c r="C16" s="238"/>
       <c r="D16" s="239"/>
-      <c r="E16" s="240"/>
-      <c r="F16" s="241"/>
+      <c r="E16" s="636"/>
+      <c r="F16" s="637"/>
       <c r="G16" s="238"/>
       <c r="H16" s="233"/>
       <c r="I16" s="234"/>
       <c r="J16" s="235"/>
       <c r="K16" s="232"/>
       <c r="L16" s="232"/>
-      <c r="M16" s="236"/>
+      <c r="M16" s="635"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
@@ -28682,15 +28789,15 @@
       <c r="B17" s="228"/>
       <c r="C17" s="229"/>
       <c r="D17" s="228"/>
-      <c r="E17" s="230"/>
-      <c r="F17" s="231"/>
+      <c r="E17" s="633"/>
+      <c r="F17" s="634"/>
       <c r="G17" s="232"/>
       <c r="H17" s="233"/>
       <c r="I17" s="234"/>
       <c r="J17" s="235"/>
       <c r="K17" s="232"/>
       <c r="L17" s="238"/>
-      <c r="M17" s="236"/>
+      <c r="M17" s="635"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
@@ -28709,15 +28816,15 @@
       <c r="B18" s="228"/>
       <c r="C18" s="229"/>
       <c r="D18" s="228"/>
-      <c r="E18" s="230"/>
-      <c r="F18" s="231"/>
+      <c r="E18" s="633"/>
+      <c r="F18" s="634"/>
       <c r="G18" s="232"/>
       <c r="H18" s="233"/>
       <c r="I18" s="234"/>
       <c r="J18" s="235"/>
       <c r="K18" s="238"/>
       <c r="L18" s="238"/>
-      <c r="M18" s="236"/>
+      <c r="M18" s="635"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
@@ -28736,15 +28843,15 @@
       <c r="B19" s="228"/>
       <c r="C19" s="229"/>
       <c r="D19" s="228"/>
-      <c r="E19" s="230"/>
-      <c r="F19" s="231"/>
+      <c r="E19" s="633"/>
+      <c r="F19" s="634"/>
       <c r="G19" s="232"/>
       <c r="H19" s="233"/>
       <c r="I19" s="234"/>
       <c r="J19" s="235"/>
       <c r="K19" s="232"/>
       <c r="L19" s="242"/>
-      <c r="M19" s="236"/>
+      <c r="M19" s="635"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
@@ -28762,16 +28869,16 @@
       <c r="A20" s="53"/>
       <c r="B20" s="228"/>
       <c r="C20" s="229"/>
-      <c r="D20" s="243"/>
-      <c r="E20" s="230"/>
-      <c r="F20" s="231"/>
+      <c r="D20" s="228"/>
+      <c r="E20" s="633"/>
+      <c r="F20" s="634"/>
       <c r="G20" s="232"/>
       <c r="H20" s="233"/>
       <c r="I20" s="234"/>
       <c r="J20" s="235"/>
       <c r="K20" s="232"/>
       <c r="L20" s="238"/>
-      <c r="M20" s="236"/>
+      <c r="M20" s="635"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
@@ -28789,16 +28896,16 @@
       <c r="A21" s="53"/>
       <c r="B21" s="228"/>
       <c r="C21" s="229"/>
-      <c r="D21" s="243"/>
-      <c r="E21" s="230"/>
-      <c r="F21" s="231"/>
+      <c r="D21" s="228"/>
+      <c r="E21" s="633"/>
+      <c r="F21" s="634"/>
       <c r="G21" s="232"/>
       <c r="H21" s="233"/>
       <c r="I21" s="234"/>
       <c r="J21" s="235"/>
       <c r="K21" s="232"/>
       <c r="L21" s="232"/>
-      <c r="M21" s="236"/>
+      <c r="M21" s="635"/>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
@@ -28816,16 +28923,16 @@
       <c r="A22" s="53"/>
       <c r="B22" s="228"/>
       <c r="C22" s="229"/>
-      <c r="D22" s="243"/>
-      <c r="E22" s="230"/>
-      <c r="F22" s="231"/>
+      <c r="D22" s="228"/>
+      <c r="E22" s="633"/>
+      <c r="F22" s="634"/>
       <c r="G22" s="232"/>
       <c r="H22" s="233"/>
       <c r="I22" s="234"/>
       <c r="J22" s="235"/>
       <c r="K22" s="232"/>
       <c r="L22" s="242"/>
-      <c r="M22" s="236"/>
+      <c r="M22" s="635"/>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
@@ -28843,16 +28950,16 @@
       <c r="A23" s="53"/>
       <c r="B23" s="228"/>
       <c r="C23" s="229"/>
-      <c r="D23" s="243"/>
-      <c r="E23" s="230"/>
-      <c r="F23" s="231"/>
+      <c r="D23" s="228"/>
+      <c r="E23" s="633"/>
+      <c r="F23" s="634"/>
       <c r="G23" s="232"/>
       <c r="H23" s="233"/>
       <c r="I23" s="234"/>
       <c r="J23" s="235"/>
       <c r="K23" s="232"/>
       <c r="L23" s="244"/>
-      <c r="M23" s="236"/>
+      <c r="M23" s="635"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
@@ -28870,16 +28977,16 @@
       <c r="A24" s="53"/>
       <c r="B24" s="228"/>
       <c r="C24" s="229"/>
-      <c r="D24" s="243"/>
-      <c r="E24" s="230"/>
-      <c r="F24" s="231"/>
+      <c r="D24" s="228"/>
+      <c r="E24" s="633"/>
+      <c r="F24" s="634"/>
       <c r="G24" s="232"/>
       <c r="H24" s="233"/>
       <c r="I24" s="234"/>
       <c r="J24" s="235"/>
       <c r="K24" s="232"/>
       <c r="L24" s="244"/>
-      <c r="M24" s="236"/>
+      <c r="M24" s="635"/>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
@@ -29595,7 +29702,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -30268,7 +30375,7 @@
       <c r="A4" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="632" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="3"/>
@@ -30277,7 +30384,7 @@
       <c r="F4" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="G4" s="214"/>
+      <c r="G4" s="631"/>
       <c r="H4" s="214"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
@@ -30340,7 +30447,7 @@
       <c r="F6" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="G6" s="335" t="s">
+      <c r="G6" s="647" t="s">
         <v>25</v>
       </c>
       <c r="H6" s="3"/>
